--- a/AtchisonRegime/Outputs/China/China_Eq/df_regTrendSummaryChina_Eq.xlsx
+++ b/AtchisonRegime/Outputs/China/China_Eq/df_regTrendSummaryChina_Eq.xlsx
@@ -780,13 +780,13 @@
         <v>45626</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1864685281693315</v>
+        <v>0.2074307555318788</v>
       </c>
     </row>
   </sheetData>
